--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4099,7 +4099,7 @@
         <v>85</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>86</v>
@@ -5001,7 +5001,7 @@
         <v>79</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>77</v>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,6 +237,9 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
     <t>Mapping: RIM Mapping</t>
   </si>
   <si>
@@ -244,9 +247,6 @@
   </si>
   <si>
     <t>Mapping: UDI Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
   </si>
   <si>
     <t/>
@@ -574,6 +574,9 @@
     <t>The device identifier (DI) is a mandatory, fixed portion of a UDI that identifies the labeler and the specific version or model of a device.</t>
   </si>
   <si>
+    <t>1353: target not supported</t>
+  </si>
+  <si>
     <t>Role.id.extension</t>
   </si>
   <si>
@@ -581,9 +584,6 @@
   </si>
   <si>
     <t>The device identifier (DI), a mandatory, fixed portion of a UDI that identifies the labeler and the specific version or model of a device.</t>
-  </si>
-  <si>
-    <t>1353: target not supported</t>
   </si>
   <si>
     <t>Device.udiCarrier.issuer</t>
@@ -720,13 +720,13 @@
     <t>http://hl7.org/fhir/ValueSet/device-status|4.0.1</t>
   </si>
   <si>
+    <t>1355: target not supported</t>
+  </si>
+  <si>
     <t>.statusCode</t>
   </si>
   <si>
     <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>1355: target not supported</t>
   </si>
   <si>
     <t>Device.statusReason</t>
@@ -767,13 +767,13 @@
     <t>For example, this applies to devices in the United States regulated under *Code of Federal Regulation 21CFR§1271.290(c)*.</t>
   </si>
   <si>
+    <t>1363: target not supported</t>
+  </si>
+  <si>
     <t>.lotNumberText</t>
   </si>
   <si>
     <t>The lot or batch number within which a device was manufactured - which is a component of the production identifier (PI), a conditional, variable portion of a UDI.</t>
-  </si>
-  <si>
-    <t>1363: target not supported</t>
   </si>
   <si>
     <t>Device.manufacturer</t>
@@ -801,15 +801,15 @@
     <t>The date and time when the device was manufactured.</t>
   </si>
   <si>
+    <t>1371: target not supported</t>
+  </si>
+  <si>
     <t>.existenceTime.low</t>
   </si>
   <si>
     <t>The date a specific device was manufactured - which is a component of the production identifier (PI), a conditional, variable portion of a UDI.  For FHIR, The datetime syntax must converted to YYYY-MM-DD[THH:MM:SS].  If hour is present, the minutes and seconds should both be set to “00”.</t>
   </si>
   <si>
-    <t>1371: target not supported</t>
-  </si>
-  <si>
     <t>Device.expirationDate</t>
   </si>
   <si>
@@ -819,15 +819,15 @@
     <t>The date and time beyond which this device is no longer valid or should not be used (if applicable).</t>
   </si>
   <si>
+    <t>1374: target not supported</t>
+  </si>
+  <si>
     <t>.expirationTime</t>
   </si>
   <si>
     <t>the expiration date of a specific device -  which is a component of the production identifier (PI), a conditional, variable portion of a UDI.  For FHIR, The datetime syntax must converted to YYYY-MM-DD[THH:MM:SS].  If hour is present, the minutes and seconds should both be set to “00”.</t>
   </si>
   <si>
-    <t>1374: target not supported</t>
-  </si>
-  <si>
     <t>Device.lotNumber</t>
   </si>
   <si>
@@ -852,10 +852,10 @@
     <t>Alphanumeric Maximum 20.</t>
   </si>
   <si>
+    <t>1381: target not supported</t>
+  </si>
+  <si>
     <t>.playedRole[typeCode=MANU].id</t>
-  </si>
-  <si>
-    <t>1381: target not supported</t>
   </si>
   <si>
     <t>Device.deviceName</t>
@@ -1564,10 +1564,10 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="61.40234375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="88.6875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="61.40234375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1794,10 +1794,10 @@
         <v>83</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL2" t="s" s="2">
         <v>30</v>
-      </c>
-      <c r="AL2" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM2" t="s" s="2">
         <v>77</v>
@@ -2362,10 +2362,10 @@
         <v>97</v>
       </c>
       <c r="AK7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL7" t="s" s="2">
         <v>120</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>77</v>
@@ -2476,10 +2476,10 @@
         <v>77</v>
       </c>
       <c r="AK8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL8" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="AL8" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>77</v>
@@ -2590,10 +2590,10 @@
         <v>136</v>
       </c>
       <c r="AK9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL9" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="AL9" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>77</v>
@@ -2706,10 +2706,10 @@
         <v>136</v>
       </c>
       <c r="AK10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL10" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="AL10" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>77</v>
@@ -2820,16 +2820,16 @@
         <v>97</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL11" t="s" s="2">
         <v>147</v>
       </c>
-      <c r="AL11" t="s" s="2">
+      <c r="AM11" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="AN11" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="12" hidden="true">
@@ -3046,13 +3046,13 @@
         <v>97</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL13" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="AL13" t="s" s="2">
+      <c r="AM13" t="s" s="2">
         <v>148</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>77</v>
@@ -3158,10 +3158,10 @@
         <v>77</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL14" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>77</v>
@@ -3272,10 +3272,10 @@
         <v>136</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL15" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>77</v>
@@ -3388,10 +3388,10 @@
         <v>136</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL16" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
@@ -3612,16 +3612,16 @@
         <v>97</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL18" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="AL18" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="AM18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN18" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="19" hidden="true">
@@ -3726,10 +3726,10 @@
         <v>97</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL19" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -3840,16 +3840,16 @@
         <v>97</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>77</v>
+        <v>179</v>
       </c>
       <c r="AM20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN20" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="21" hidden="true">
@@ -3954,16 +3954,16 @@
         <v>97</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>77</v>
+        <v>179</v>
       </c>
       <c r="AM21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="22" hidden="true">
@@ -4068,10 +4068,10 @@
         <v>97</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL22" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="AL22" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
@@ -4188,10 +4188,10 @@
         <v>221</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>77</v>
+        <v>222</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>222</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" hidden="true">
@@ -4297,10 +4297,10 @@
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>221</v>
+        <v>77</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>77</v>
+        <v>222</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>77</v>
@@ -4411,10 +4411,10 @@
         <v>235</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>179</v>
+        <v>236</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>236</v>
+        <v>180</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>237</v>
@@ -4520,16 +4520,16 @@
         <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL26" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="AL26" t="s" s="2">
-        <v>179</v>
-      </c>
       <c r="AM26" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="27" hidden="true">
@@ -4635,10 +4635,10 @@
         <v>246</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>247</v>
+        <v>180</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>248</v>
@@ -4747,10 +4747,10 @@
         <v>252</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>179</v>
+        <v>253</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>253</v>
+        <v>180</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>254</v>
@@ -4856,16 +4856,16 @@
         <v>97</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>179</v>
+        <v>236</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>236</v>
+        <v>180</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>258</v>
+        <v>237</v>
       </c>
     </row>
     <row r="30" hidden="true">
@@ -4973,13 +4973,13 @@
         <v>263</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>179</v>
+        <v>264</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>264</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" hidden="true">
@@ -5082,7 +5082,7 @@
         <v>97</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>77</v>
+        <v>268</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>77</v>
@@ -5091,7 +5091,7 @@
         <v>77</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>268</v>
+        <v>77</v>
       </c>
     </row>
     <row r="32" hidden="true">
@@ -5194,10 +5194,10 @@
         <v>77</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL32" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
@@ -5308,10 +5308,10 @@
         <v>136</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL33" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
@@ -5424,10 +5424,10 @@
         <v>136</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL34" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="AL34" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
@@ -5648,13 +5648,13 @@
         <v>97</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL36" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="AL36" t="s" s="2">
-        <v>179</v>
-      </c>
       <c r="AM36" t="s" s="2">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>77</v>
@@ -5760,13 +5760,13 @@
         <v>97</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL37" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AL37" t="s" s="2">
-        <v>179</v>
-      </c>
       <c r="AM37" t="s" s="2">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>77</v>
@@ -5874,13 +5874,13 @@
         <v>97</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>263</v>
+        <v>77</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>179</v>
+        <v>264</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>77</v>
@@ -6210,10 +6210,10 @@
         <v>77</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL41" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -6324,10 +6324,10 @@
         <v>136</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL42" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AL42" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -6440,10 +6440,10 @@
         <v>136</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>77</v>
@@ -6667,10 +6667,10 @@
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>179</v>
+        <v>77</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>77</v>
@@ -6888,10 +6888,10 @@
         <v>77</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL47" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
@@ -7002,10 +7002,10 @@
         <v>136</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL48" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
@@ -7118,10 +7118,10 @@
         <v>136</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL49" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
@@ -7345,10 +7345,10 @@
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>179</v>
+        <v>77</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>77</v>
@@ -7678,10 +7678,10 @@
         <v>77</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL54" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
@@ -7792,10 +7792,10 @@
         <v>136</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL55" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
@@ -7908,10 +7908,10 @@
         <v>136</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL56" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
@@ -8358,13 +8358,13 @@
         <v>97</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL60" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="AL60" t="s" s="2">
+      <c r="AM60" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>77</v>
@@ -8470,13 +8470,13 @@
         <v>97</v>
       </c>
       <c r="AK61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL61" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="AL61" t="s" s="2">
+      <c r="AM61" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>77</v>
@@ -8584,13 +8584,13 @@
         <v>97</v>
       </c>
       <c r="AK62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL62" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AL62" t="s" s="2">
+      <c r="AM62" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>77</v>
@@ -8698,13 +8698,13 @@
         <v>97</v>
       </c>
       <c r="AK63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL63" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="AL63" t="s" s="2">
+      <c r="AM63" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>77</v>
@@ -8812,13 +8812,13 @@
         <v>97</v>
       </c>
       <c r="AK64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL64" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="AL64" t="s" s="2">
+      <c r="AM64" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>77</v>
@@ -8924,10 +8924,10 @@
         <v>97</v>
       </c>
       <c r="AK65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL65" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>77</v>
@@ -9036,10 +9036,10 @@
         <v>97</v>
       </c>
       <c r="AK66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL66" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>77</v>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2425" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2425" uniqueCount="381">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -120,7 +120,7 @@
     <t>Abstract</t>
   </si>
   <si>
-    <t>false</t>
+    <t>true</t>
   </si>
   <si>
     <t>Derivation</t>
@@ -673,6 +673,9 @@
   </si>
   <si>
     <t>If separate barcodes for DI and PI are present, concatenate the string with DI first and in order of human readable expression on label.</t>
+  </si>
+  <si>
+    <t>1794: target not supported</t>
   </si>
   <si>
     <t>A unique device identifier (UDI) on a device label in plain text</t>
@@ -3954,7 +3957,7 @@
         <v>97</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>77</v>
+        <v>205</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>179</v>
@@ -3963,15 +3966,15 @@
         <v>77</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3997,14 +4000,14 @@
         <v>105</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -4029,13 +4032,13 @@
         <v>77</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>77</v>
@@ -4053,7 +4056,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4071,7 +4074,7 @@
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
@@ -4082,10 +4085,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4111,13 +4114,13 @@
         <v>105</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4143,13 +4146,13 @@
         <v>77</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>77</v>
@@ -4167,7 +4170,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4182,13 +4185,13 @@
         <v>97</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>77</v>
@@ -4196,10 +4199,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4222,13 +4225,13 @@
         <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4255,13 +4258,13 @@
         <v>77</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>77</v>
@@ -4279,7 +4282,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4300,7 +4303,7 @@
         <v>77</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>77</v>
@@ -4308,14 +4311,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4337,13 +4340,13 @@
         <v>161</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4393,7 +4396,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4408,24 +4411,24 @@
         <v>97</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>180</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4451,10 +4454,10 @@
         <v>161</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4505,7 +4508,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4523,7 +4526,7 @@
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>180</v>
@@ -4534,10 +4537,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4560,13 +4563,13 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4617,7 +4620,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4632,24 +4635,24 @@
         <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>180</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4672,13 +4675,13 @@
         <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4729,7 +4732,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4744,24 +4747,24 @@
         <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>180</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4787,10 +4790,10 @@
         <v>161</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4841,7 +4844,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4856,24 +4859,24 @@
         <v>97</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>180</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4899,13 +4902,13 @@
         <v>161</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4955,7 +4958,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4970,10 +4973,10 @@
         <v>97</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>180</v>
@@ -4984,10 +4987,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5013,10 +5016,10 @@
         <v>155</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5067,7 +5070,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5082,7 +5085,7 @@
         <v>97</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>77</v>
@@ -5096,10 +5099,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5208,10 +5211,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5322,10 +5325,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5438,14 +5441,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5467,10 +5470,10 @@
         <v>161</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5521,7 +5524,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>85</v>
@@ -5550,10 +5553,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5579,10 +5582,10 @@
         <v>105</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5609,13 +5612,13 @@
         <v>77</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>77</v>
@@ -5633,7 +5636,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>85</v>
@@ -5651,7 +5654,7 @@
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>180</v>
@@ -5662,10 +5665,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5691,10 +5694,10 @@
         <v>161</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5745,7 +5748,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5763,7 +5766,7 @@
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>180</v>
@@ -5774,10 +5777,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5803,13 +5806,13 @@
         <v>161</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5859,7 +5862,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5877,7 +5880,7 @@
         <v>77</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>180</v>
@@ -5888,10 +5891,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5914,13 +5917,13 @@
         <v>77</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5947,13 +5950,13 @@
         <v>77</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>77</v>
@@ -5971,7 +5974,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6000,10 +6003,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6029,10 +6032,10 @@
         <v>155</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6083,7 +6086,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6112,10 +6115,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6224,10 +6227,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6338,10 +6341,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6454,14 +6457,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6480,13 +6483,13 @@
         <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6537,7 +6540,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>85</v>
@@ -6566,10 +6569,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6595,10 +6598,10 @@
         <v>161</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6649,7 +6652,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6678,10 +6681,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6707,10 +6710,10 @@
         <v>155</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6761,7 +6764,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6790,10 +6793,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6902,10 +6905,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7016,10 +7019,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7132,14 +7135,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7158,13 +7161,13 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7215,7 +7218,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7244,10 +7247,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7273,10 +7276,10 @@
         <v>143</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7327,7 +7330,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7356,10 +7359,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7385,10 +7388,10 @@
         <v>161</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7439,7 +7442,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>85</v>
@@ -7468,10 +7471,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7497,10 +7500,10 @@
         <v>155</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7551,7 +7554,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7580,10 +7583,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7692,10 +7695,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7806,10 +7809,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7922,10 +7925,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7948,13 +7951,13 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8005,7 +8008,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>85</v>
@@ -8034,10 +8037,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8060,13 +8063,13 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8117,7 +8120,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8146,10 +8149,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8172,13 +8175,13 @@
         <v>77</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8229,7 +8232,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8258,10 +8261,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8284,17 +8287,17 @@
         <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>77</v>
@@ -8343,7 +8346,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8361,10 +8364,10 @@
         <v>77</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>77</v>
@@ -8372,10 +8375,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8398,13 +8401,13 @@
         <v>77</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8455,7 +8458,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8473,10 +8476,10 @@
         <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>77</v>
@@ -8484,10 +8487,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8510,16 +8513,16 @@
         <v>77</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8569,7 +8572,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8587,10 +8590,10 @@
         <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>77</v>
@@ -8598,10 +8601,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8624,17 +8627,17 @@
         <v>77</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -8683,7 +8686,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -8701,10 +8704,10 @@
         <v>77</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>77</v>
@@ -8712,10 +8715,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8741,13 +8744,13 @@
         <v>99</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8797,7 +8800,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -8815,10 +8818,10 @@
         <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>77</v>
@@ -8826,10 +8829,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8852,13 +8855,13 @@
         <v>77</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8909,7 +8912,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -8927,7 +8930,7 @@
         <v>77</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>77</v>
@@ -8938,10 +8941,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8964,13 +8967,13 @@
         <v>86</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9021,7 +9024,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9039,7 +9042,7 @@
         <v>77</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>77</v>
@@ -9050,10 +9053,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9076,13 +9079,13 @@
         <v>77</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9133,7 +9136,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file undefined (#undefined) to us-core-implantable-device</t>
+    <t>This StructureDefinition contains the maps for VistA file undefined (undefined) to us-core-implantable-device</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-21T15:05:18+00:00</t>
+    <t>2024-07-09T16:26:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file undefined (undefined) to us-core-implantable-device</t>
+    <t>This StructureDefinition contains the maps for VistA file undefined (undefined) to us-core-implantable-device.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2425" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2425" uniqueCount="380">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -868,9 +868,6 @@
   </si>
   <si>
     <t>This represents the manufacturer's name of the device as provided by the device, from a UDI label, or by a person describing the Device.  This typically would be used when a person provides the name(s) or when the device represents one of the names available from DeviceDefinition.</t>
-  </si>
-  <si>
-    <t>1386: target not supported</t>
   </si>
   <si>
     <t>Device.deviceName.id</t>
@@ -5085,7 +5082,7 @@
         <v>97</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>269</v>
+        <v>77</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>77</v>
@@ -5099,10 +5096,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5211,10 +5208,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5325,10 +5322,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5441,14 +5438,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5470,10 +5467,10 @@
         <v>161</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5524,7 +5521,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>85</v>
@@ -5553,10 +5550,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5582,10 +5579,10 @@
         <v>105</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5615,11 +5612,11 @@
         <v>211</v>
       </c>
       <c r="Y36" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="Z36" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="Z36" t="s" s="2">
-        <v>281</v>
-      </c>
       <c r="AA36" t="s" s="2">
         <v>77</v>
       </c>
@@ -5636,7 +5633,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>85</v>
@@ -5654,7 +5651,7 @@
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>180</v>
@@ -5665,10 +5662,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5694,10 +5691,10 @@
         <v>161</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5748,7 +5745,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5766,7 +5763,7 @@
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>180</v>
@@ -5777,10 +5774,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5806,10 +5803,10 @@
         <v>161</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="N38" t="s" s="2">
         <v>263</v>
@@ -5862,7 +5859,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5891,10 +5888,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5920,10 +5917,10 @@
         <v>225</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5953,11 +5950,11 @@
         <v>228</v>
       </c>
       <c r="Y39" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="Z39" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="Z39" t="s" s="2">
-        <v>294</v>
-      </c>
       <c r="AA39" t="s" s="2">
         <v>77</v>
       </c>
@@ -5974,7 +5971,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6003,10 +6000,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6032,10 +6029,10 @@
         <v>155</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6086,7 +6083,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6115,10 +6112,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6227,10 +6224,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6341,10 +6338,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6457,14 +6454,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6486,10 +6483,10 @@
         <v>225</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6540,7 +6537,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>85</v>
@@ -6569,10 +6566,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6598,10 +6595,10 @@
         <v>161</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6652,7 +6649,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6681,10 +6678,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6710,10 +6707,10 @@
         <v>155</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6764,7 +6761,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6793,10 +6790,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6905,10 +6902,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7019,10 +7016,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7135,14 +7132,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7164,10 +7161,10 @@
         <v>225</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7218,7 +7215,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7247,10 +7244,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7276,10 +7273,10 @@
         <v>143</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7330,7 +7327,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7359,10 +7356,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7388,10 +7385,10 @@
         <v>161</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7442,7 +7439,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>85</v>
@@ -7471,10 +7468,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7500,10 +7497,10 @@
         <v>155</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7554,7 +7551,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7583,10 +7580,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7695,10 +7692,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7809,10 +7806,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7925,10 +7922,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7954,10 +7951,10 @@
         <v>225</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8008,7 +8005,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>85</v>
@@ -8037,10 +8034,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8063,13 +8060,13 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8120,7 +8117,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8149,10 +8146,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8178,10 +8175,10 @@
         <v>225</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8232,7 +8229,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8261,10 +8258,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8287,17 +8284,17 @@
         <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>77</v>
@@ -8346,7 +8343,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8364,10 +8361,10 @@
         <v>77</v>
       </c>
       <c r="AL60" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AM60" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>77</v>
@@ -8375,10 +8372,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8401,13 +8398,13 @@
         <v>77</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8458,7 +8455,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8476,10 +8473,10 @@
         <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AM61" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>77</v>
@@ -8487,10 +8484,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8513,16 +8510,16 @@
         <v>77</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8572,7 +8569,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8590,10 +8587,10 @@
         <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>77</v>
@@ -8601,10 +8598,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8627,17 +8624,17 @@
         <v>77</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -8686,7 +8683,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -8704,10 +8701,10 @@
         <v>77</v>
       </c>
       <c r="AL63" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AM63" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>77</v>
@@ -8715,10 +8712,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8744,13 +8741,13 @@
         <v>99</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8800,7 +8797,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -8818,10 +8815,10 @@
         <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>77</v>
@@ -8829,10 +8826,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8855,13 +8852,13 @@
         <v>77</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8912,7 +8909,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -8930,7 +8927,7 @@
         <v>77</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>77</v>
@@ -8941,10 +8938,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8970,10 +8967,10 @@
         <v>225</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9024,7 +9021,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9053,10 +9050,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9079,13 +9076,13 @@
         <v>77</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="L67" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="M67" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9136,7 +9133,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
